--- a/artfynd/A 31766-2026 artfynd.xlsx
+++ b/artfynd/A 31766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189359</v>
       </c>
       <c r="B2" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189361</v>
       </c>
       <c r="B3" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189342</v>
       </c>
       <c r="B4" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189331</v>
       </c>
       <c r="B6" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189366</v>
       </c>
       <c r="B7" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31766-2026 artfynd.xlsx
+++ b/artfynd/A 31766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189359</v>
       </c>
       <c r="B2" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189361</v>
       </c>
       <c r="B3" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189342</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189350</v>
       </c>
       <c r="B5" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189331</v>
       </c>
       <c r="B6" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189366</v>
       </c>
       <c r="B7" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189337</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189344</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189348</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136189330</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136189332</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136189333</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>136189336</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136189341</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136189343</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136189349</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136189352</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136189356</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>136189358</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136189365</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31766-2026 artfynd.xlsx
+++ b/artfynd/A 31766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189359</v>
       </c>
       <c r="B2" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189361</v>
       </c>
       <c r="B3" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189342</v>
       </c>
       <c r="B4" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189350</v>
       </c>
       <c r="B5" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189331</v>
       </c>
       <c r="B6" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189366</v>
       </c>
       <c r="B7" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189337</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189344</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189348</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136189330</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136189332</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136189333</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>136189336</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136189341</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136189343</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136189349</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136189352</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136189356</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>136189358</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136189365</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31766-2026 artfynd.xlsx
+++ b/artfynd/A 31766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189359</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189361</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189342</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189350</v>
       </c>
       <c r="B5" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189331</v>
       </c>
       <c r="B6" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189366</v>
       </c>
       <c r="B7" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189337</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189344</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189348</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136189330</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136189332</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136189333</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>136189336</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136189341</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136189343</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136189349</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136189352</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136189356</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>136189358</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136189365</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31766-2026 artfynd.xlsx
+++ b/artfynd/A 31766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189359</v>
       </c>
       <c r="B2" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189361</v>
       </c>
       <c r="B3" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189342</v>
       </c>
       <c r="B4" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189350</v>
       </c>
       <c r="B5" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189331</v>
       </c>
       <c r="B6" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189366</v>
       </c>
       <c r="B7" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189337</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189344</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189348</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31766-2026 artfynd.xlsx
+++ b/artfynd/A 31766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189359</v>
       </c>
       <c r="B2" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189361</v>
       </c>
       <c r="B3" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189342</v>
       </c>
       <c r="B4" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189350</v>
       </c>
       <c r="B5" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189331</v>
       </c>
       <c r="B6" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189366</v>
       </c>
       <c r="B7" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189337</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189344</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189348</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136189330</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136189332</v>
       </c>
       <c r="B12" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136189333</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>136189336</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136189341</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136189343</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136189349</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136189352</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136189356</v>
       </c>
       <c r="B19" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>136189358</v>
       </c>
       <c r="B20" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136189365</v>
       </c>
       <c r="B21" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31766-2026 artfynd.xlsx
+++ b/artfynd/A 31766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189359</v>
       </c>
       <c r="B2" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189361</v>
       </c>
       <c r="B3" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189342</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189331</v>
       </c>
       <c r="B6" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189366</v>
       </c>
       <c r="B7" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31766-2026 artfynd.xlsx
+++ b/artfynd/A 31766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189359</v>
       </c>
       <c r="B2" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189361</v>
       </c>
       <c r="B3" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189342</v>
       </c>
       <c r="B4" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189350</v>
       </c>
       <c r="B5" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189331</v>
       </c>
       <c r="B6" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189366</v>
       </c>
       <c r="B7" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189337</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189344</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189348</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136189330</v>
       </c>
       <c r="B11" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136189332</v>
       </c>
       <c r="B12" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136189333</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>136189336</v>
       </c>
       <c r="B14" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136189341</v>
       </c>
       <c r="B15" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136189343</v>
       </c>
       <c r="B16" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136189349</v>
       </c>
       <c r="B17" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136189352</v>
       </c>
       <c r="B18" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136189356</v>
       </c>
       <c r="B19" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>136189358</v>
       </c>
       <c r="B20" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136189365</v>
       </c>
       <c r="B21" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31766-2026 artfynd.xlsx
+++ b/artfynd/A 31766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189359</v>
       </c>
       <c r="B2" t="n">
-        <v>92097</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136189361</v>
       </c>
       <c r="B3" t="n">
-        <v>92097</v>
+        <v>92098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136189342</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136189350</v>
       </c>
       <c r="B5" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136189331</v>
       </c>
       <c r="B6" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136189366</v>
       </c>
       <c r="B7" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136189337</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136189344</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136189348</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
